--- a/FMBrandFY2027CounterBudgetStatisticsTable.xlsx
+++ b/FMBrandFY2027CounterBudgetStatisticsTable.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VBACostCenterSplit\costcentersplit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5543A0BB-9685-4E4E-AEF1-F1E5C963DBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0E513A9-EB14-4265-8357-AC53C4CA32CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{B2BD2BF4-A052-40EA-B7F1-6A00E5EC2EF2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{57E4E20F-37E1-4418-84BF-A616576BE091}"/>
   </bookViews>
   <sheets>
     <sheet name="CostCenterGroupBySumResult" sheetId="1" r:id="rId1"/>
@@ -873,8 +873,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33363F0F-9564-421D-9776-87614D7C680A}">
-  <sheetPr codeName="Sheet14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC12E5B2-D26C-44CD-96E6-134BFAF28FA4}">
   <dimension ref="A1:BE36"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/FMBrandFY2027CounterBudgetStatisticsTable.xlsx
+++ b/FMBrandFY2027CounterBudgetStatisticsTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VBACostCenterSplit\costcentersplit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHENKA~1\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0E513A9-EB14-4265-8357-AC53C4CA32CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EEC3216-A880-4C9E-BA12-6C381CD6BEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{57E4E20F-37E1-4418-84BF-A616576BE091}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{ADC3FF18-4ABA-4253-925A-B75EE1738F68}"/>
   </bookViews>
   <sheets>
     <sheet name="CostCenterGroupBySumResult" sheetId="1" r:id="rId1"/>
@@ -873,7 +873,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC12E5B2-D26C-44CD-96E6-134BFAF28FA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96DA6B4A-CE6E-45B3-BA4C-A9858B48BDE6}">
   <dimension ref="A1:BE36"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/FMBrandFY2027CounterBudgetStatisticsTable.xlsx
+++ b/FMBrandFY2027CounterBudgetStatisticsTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHENKA~1\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EEC3216-A880-4C9E-BA12-6C381CD6BEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33FEC6EC-D5D1-4B53-8B4D-4ED756021F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{ADC3FF18-4ABA-4253-925A-B75EE1738F68}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{A76856D6-4B57-4488-951A-5C8856EDB3C9}"/>
   </bookViews>
   <sheets>
     <sheet name="CostCenterGroupBySumResult" sheetId="1" r:id="rId1"/>
@@ -390,7 +390,7 @@
     <t>KLFMFY2022000012</t>
   </si>
   <si>
-    <t>合计：</t>
+    <t>Total：</t>
   </si>
   <si>
     <t>KL</t>
@@ -415,7 +415,7 @@
     <t>KLFMFY2026000002</t>
   </si>
   <si>
-    <t>KL合计：</t>
+    <t>KL Total：</t>
   </si>
   <si>
     <t>上海国金中心</t>
@@ -430,7 +430,7 @@
     <t>KLFMFY2026000006</t>
   </si>
   <si>
-    <t>FM合计：</t>
+    <t>FM Total：</t>
   </si>
 </sst>
 </file>
@@ -873,7 +873,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96DA6B4A-CE6E-45B3-BA4C-A9858B48BDE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDB7382F-813E-46EC-890C-8725F487AFB4}">
   <dimension ref="A1:BE36"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/FMBrandFY2027CounterBudgetStatisticsTable.xlsx
+++ b/FMBrandFY2027CounterBudgetStatisticsTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHENKA~1\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shenkailing\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33FEC6EC-D5D1-4B53-8B4D-4ED756021F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0F8A6DB-8BC4-42DA-8D75-CF1B94DD74FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{A76856D6-4B57-4488-951A-5C8856EDB3C9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17620" xr2:uid="{6B5BD3F6-4FA0-432C-847D-E9844506560F}"/>
   </bookViews>
   <sheets>
     <sheet name="CostCenterGroupBySumResult" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -390,7 +387,7 @@
     <t>KLFMFY2022000012</t>
   </si>
   <si>
-    <t>Total：</t>
+    <t>Total:</t>
   </si>
   <si>
     <t>KL</t>
@@ -415,7 +412,7 @@
     <t>KLFMFY2026000002</t>
   </si>
   <si>
-    <t>KL Total：</t>
+    <t>KL Total:</t>
   </si>
   <si>
     <t>上海国金中心</t>
@@ -430,7 +427,7 @@
     <t>KLFMFY2026000006</t>
   </si>
   <si>
-    <t>FM Total：</t>
+    <t>FM Total:</t>
   </si>
 </sst>
 </file>
@@ -873,7 +870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDB7382F-813E-46EC-890C-8725F487AFB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2330014-84B6-4D09-B749-9A1EAA999106}">
   <dimension ref="A1:BE36"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/FMBrandFY2027CounterBudgetStatisticsTable.xlsx
+++ b/FMBrandFY2027CounterBudgetStatisticsTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shenkailing\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0F8A6DB-8BC4-42DA-8D75-CF1B94DD74FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{999058A1-1E7C-4140-8D92-97E8F1115675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17620" xr2:uid="{6B5BD3F6-4FA0-432C-847D-E9844506560F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17620" xr2:uid="{63FD8C7A-52A4-4BF2-9B6D-9216AF1DAA34}"/>
   </bookViews>
   <sheets>
     <sheet name="CostCenterGroupBySumResult" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -870,7 +873,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2330014-84B6-4D09-B749-9A1EAA999106}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{359CBEFD-39F1-4025-A4A9-AD83E69D86DF}">
   <dimension ref="A1:BE36"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
